--- a/data/mini-example-resilience/Power_VRES.xlsx
+++ b/data/mini-example-resilience/Power_VRES.xlsx
@@ -5,17 +5,30 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Simon Malacek\Code\LEGO-Pyomo\data\Mini-example-resilience\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Simon Malacek\Code\LEGO-Pyomo\data\mini-example-resilience\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA269025-F5C2-452C-81EF-A7FA4AC240B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CC92DA0-85DE-46EB-AB55-6E203CD7FDE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ScenarioA" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1170,25 +1183,25 @@
         <v>75</v>
       </c>
       <c r="F8" s="13">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="G8" s="14">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="H8" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" s="13">
-        <v>290</v>
+        <v>10</v>
       </c>
       <c r="J8" s="15">
-        <v>72641.801500000001</v>
+        <v>200</v>
       </c>
       <c r="K8" s="15">
         <v>2</v>
       </c>
       <c r="L8" s="16">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M8" s="14"/>
       <c r="N8" s="14"/>
